--- a/artfynd/A 14941-2026 artfynd.xlsx
+++ b/artfynd/A 14941-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132904493</v>
       </c>
       <c r="B2" t="n">
-        <v>91949</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,54 +772,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132908890</v>
+        <v>132907036</v>
       </c>
       <c r="B3" t="n">
-        <v>99140</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Moängsmossen, Ög</t>
+          <t>Pinsveden, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546744</v>
+        <v>546518</v>
       </c>
       <c r="R3" t="n">
-        <v>6425437</v>
+        <v>6425302</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132908348</v>
+        <v>132907862</v>
       </c>
       <c r="B4" t="n">
-        <v>106268</v>
+        <v>58658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +888,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Moängsmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546597</v>
+        <v>546582</v>
       </c>
       <c r="R4" t="n">
-        <v>6425514</v>
+        <v>6425420</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132904957</v>
+        <v>132904920</v>
       </c>
       <c r="B5" t="n">
-        <v>99140</v>
+        <v>99195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,7 +1012,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1019,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546667</v>
+        <v>546677</v>
       </c>
       <c r="R5" t="n">
-        <v>6425381</v>
+        <v>6425382</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,45 +1088,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132904786</v>
+        <v>132904957</v>
       </c>
       <c r="B6" t="n">
-        <v>98005</v>
+        <v>99195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Moängsmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546677</v>
+        <v>546667</v>
       </c>
       <c r="R6" t="n">
-        <v>6425382</v>
+        <v>6425381</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,56 +1194,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132907862</v>
+        <v>132908890</v>
       </c>
       <c r="B7" t="n">
-        <v>58641</v>
+        <v>99195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Moängsmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>546582</v>
+        <v>546744</v>
       </c>
       <c r="R7" t="n">
-        <v>6425420</v>
+        <v>6425437</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,53 +1300,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132907036</v>
+        <v>132908348</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>106324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pinsveden, Ög</t>
+          <t>Moängsmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546518</v>
+        <v>546597</v>
       </c>
       <c r="R8" t="n">
-        <v>6425302</v>
+        <v>6425514</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,44 +1397,35 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132904920</v>
+        <v>132904786</v>
       </c>
       <c r="B9" t="n">
-        <v>99140</v>
+        <v>98060</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Moängsmossen, Ög</t>
@@ -1491,6 +1491,103 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132905399</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Pinsveden, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>546643</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6425231</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Horn</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14941-2026 artfynd.xlsx
+++ b/artfynd/A 14941-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132904493</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132907036</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132907862</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132904920</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132904957</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132908890</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132908348</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132904786</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1588,8 +1633,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132905399</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>